--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129912929</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129913570</v>
       </c>
       <c r="B3" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129912950</v>
       </c>
       <c r="B4" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129913022</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>129912959</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129913733</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129912954</v>
       </c>
       <c r="B8" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129912929</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129913570</v>
       </c>
       <c r="B3" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129912950</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129913022</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin</t>
+          <t>August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         <v>129912959</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129913733</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129912954</v>
       </c>
       <c r="B8" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129912929</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129913570</v>
       </c>
       <c r="B3" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129912950</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin</t>
+          <t>August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
         <v>129913022</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>129912959</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin</t>
+          <t>August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
         <v>129912954</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin</t>
+          <t>August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129912929</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129913570</v>
       </c>
       <c r="B3" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129912950</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
         <v>129913022</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         <v>129912959</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
         <v>129913733</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129912954</v>
       </c>
       <c r="B8" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>August Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129913570</v>
       </c>
       <c r="B3" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129913022</v>
       </c>
       <c r="B5" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129912929</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129913570</v>
       </c>
       <c r="B3" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129912950</v>
       </c>
       <c r="B4" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129913022</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>129912959</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129913733</v>
       </c>
       <c r="B7" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129912954</v>
       </c>
       <c r="B8" t="n">
-        <v>80201</v>
+        <v>80286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83229</v>
+        <v>83230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2021 artfynd.xlsx
+++ b/artfynd/A 18731-2021 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>131157738</v>
       </c>
       <c r="B9" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
